--- a/USAstocks.xlsx
+++ b/USAstocks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TE237142\iCloudDrive\Docs Arnau\Forex\Fx2020\EvolucioInvertim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD13CFCA-B5D3-47F6-8082-4CB3825A16FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCABB18-1803-445C-B193-06157AE2C915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-1230" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>Ticker</t>
   </si>
@@ -229,6 +229,15 @@
   </si>
   <si>
     <t>Medical - Biomedical</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>Electronics - Semiconductors</t>
+  </si>
+  <si>
+    <t>Marvell Technology Inc</t>
   </si>
 </sst>
 </file>
@@ -287,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -296,6 +305,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -832,6 +843,9 @@
       <c r="E13" s="3">
         <v>46113</v>
       </c>
+      <c r="F13" s="3">
+        <v>46296</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -893,7 +907,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -910,7 +924,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -927,7 +941,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -944,49 +958,42 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="3">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="3">
-        <v>46048</v>
-      </c>
-      <c r="D22" s="3">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="3">
-        <v>46104</v>
-      </c>
-      <c r="D23" s="3">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -994,13 +1001,13 @@
         <v>63</v>
       </c>
       <c r="C24" s="3">
-        <v>46139</v>
+        <v>46048</v>
       </c>
       <c r="D24" s="3">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1008,13 +1015,13 @@
         <v>63</v>
       </c>
       <c r="C25" s="3">
-        <v>46153</v>
+        <v>46104</v>
       </c>
       <c r="D25" s="3">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1022,13 +1029,13 @@
         <v>63</v>
       </c>
       <c r="C26" s="3">
-        <v>46181</v>
+        <v>46139</v>
       </c>
       <c r="D26" s="3">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -1036,9 +1043,37 @@
         <v>63</v>
       </c>
       <c r="C27" s="3">
+        <v>46153</v>
+      </c>
+      <c r="D27" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46181</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="3">
         <v>46195</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D29" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
